--- a/BusinessAnalysis/database_design.xlsx
+++ b/BusinessAnalysis/database_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA20392E-C86B-4A46-BCFA-65FC3018D9DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65BD0785-A8C4-4D08-BA57-92E25C0D4E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{651FA330-C6EA-40A0-B0A3-026F11F4DB33}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
   <si>
     <t>user</t>
   </si>
@@ -94,6 +94,60 @@
   </si>
   <si>
     <t>authorization_role</t>
+  </si>
+  <si>
+    <t>e_bike_category_id</t>
+  </si>
+  <si>
+    <t>e_bike_category_name</t>
+  </si>
+  <si>
+    <t>ROAD</t>
+  </si>
+  <si>
+    <t>FAT_TIRE</t>
+  </si>
+  <si>
+    <t>FOLDING</t>
+  </si>
+  <si>
+    <t>CARGO</t>
+  </si>
+  <si>
+    <t>MOUNTAIN</t>
+  </si>
+  <si>
+    <t>HYBRID / TREKKING</t>
+  </si>
+  <si>
+    <t>CITY</t>
+  </si>
+  <si>
+    <t>e_bike_id</t>
+  </si>
+  <si>
+    <t>e_bike_name</t>
+  </si>
+  <si>
+    <t>supplier_id</t>
+  </si>
+  <si>
+    <t>supplier_name</t>
+  </si>
+  <si>
+    <t>supplier_type</t>
+  </si>
+  <si>
+    <t>is_verified</t>
+  </si>
+  <si>
+    <t>supplier rating</t>
+  </si>
+  <si>
+    <t>e_bike_rating</t>
+  </si>
+  <si>
+    <t>supplier_rating_id</t>
   </si>
 </sst>
 </file>
@@ -142,13 +196,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,17 +520,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C79A3F5-2569-40DD-8568-D6589AE542AA}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="23.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.6640625" customWidth="1"/>
+    <col min="5" max="5" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -489,8 +548,14 @@
       <c r="E1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -500,8 +565,20 @@
       <c r="C2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -511,60 +588,102 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E7" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E8" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E9" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C17" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C18" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C19" s="3" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/BusinessAnalysis/database_design.xlsx
+++ b/BusinessAnalysis/database_design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65BD0785-A8C4-4D08-BA57-92E25C0D4E46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB358615-8EAC-4CD7-BED3-211798C5B2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{651FA330-C6EA-40A0-B0A3-026F11F4DB33}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>user</t>
   </si>
@@ -141,13 +141,19 @@
     <t>is_verified</t>
   </si>
   <si>
-    <t>supplier rating</t>
-  </si>
-  <si>
     <t>e_bike_rating</t>
   </si>
   <si>
     <t>supplier_rating_id</t>
+  </si>
+  <si>
+    <t>supplier_rating</t>
+  </si>
+  <si>
+    <t>rating_date_time</t>
+  </si>
+  <si>
+    <t>comment</t>
   </si>
 </sst>
 </file>
@@ -552,7 +558,7 @@
         <v>14</v>
       </c>
       <c r="G1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -575,7 +581,7 @@
         <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -632,7 +638,7 @@
         <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -646,7 +652,7 @@
         <v>26</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -656,6 +662,9 @@
       <c r="E7" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -663,6 +672,9 @@
       </c>
       <c r="E8" s="4" t="s">
         <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">

--- a/BusinessAnalysis/database_design.xlsx
+++ b/BusinessAnalysis/database_design.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Micro2Move\BusinessAnalysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Micro2Move\BusinessAnalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB358615-8EAC-4CD7-BED3-211798C5B2CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{651FA330-C6EA-40A0-B0A3-026F11F4DB33}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23258" windowHeight="12458"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="124">
   <si>
     <t>user</t>
   </si>
@@ -57,9 +56,6 @@
     <t>govt_id_image_link</t>
   </si>
   <si>
-    <t>terms_conditions_accepted</t>
-  </si>
-  <si>
     <t>e_bike_category</t>
   </si>
   <si>
@@ -102,65 +98,320 @@
     <t>e_bike_category_name</t>
   </si>
   <si>
-    <t>ROAD</t>
-  </si>
-  <si>
-    <t>FAT_TIRE</t>
-  </si>
-  <si>
-    <t>FOLDING</t>
-  </si>
-  <si>
-    <t>CARGO</t>
-  </si>
-  <si>
-    <t>MOUNTAIN</t>
-  </si>
-  <si>
-    <t>HYBRID / TREKKING</t>
-  </si>
-  <si>
-    <t>CITY</t>
-  </si>
-  <si>
     <t>e_bike_id</t>
   </si>
   <si>
     <t>e_bike_name</t>
   </si>
   <si>
-    <t>supplier_id</t>
-  </si>
-  <si>
-    <t>supplier_name</t>
-  </si>
-  <si>
-    <t>supplier_type</t>
-  </si>
-  <si>
     <t>is_verified</t>
   </si>
   <si>
     <t>e_bike_rating</t>
   </si>
   <si>
-    <t>supplier_rating_id</t>
-  </si>
-  <si>
-    <t>supplier_rating</t>
-  </si>
-  <si>
     <t>rating_date_time</t>
   </si>
   <si>
     <t>comment</t>
+  </si>
+  <si>
+    <t>supplier_user_id</t>
+  </si>
+  <si>
+    <t>price_per_week</t>
+  </si>
+  <si>
+    <t>available_from_date</t>
+  </si>
+  <si>
+    <t>available_to_date</t>
+  </si>
+  <si>
+    <t>city</t>
+  </si>
+  <si>
+    <t>hybrid/ trecking</t>
+  </si>
+  <si>
+    <t>mountain</t>
+  </si>
+  <si>
+    <t>cargo</t>
+  </si>
+  <si>
+    <t>folding</t>
+  </si>
+  <si>
+    <t>fat tyre</t>
+  </si>
+  <si>
+    <t>road</t>
+  </si>
+  <si>
+    <t>tnc_accepted</t>
+  </si>
+  <si>
+    <t>pick_up_address</t>
+  </si>
+  <si>
+    <t>e_bike_status</t>
+  </si>
+  <si>
+    <t>renter_user_id</t>
+  </si>
+  <si>
+    <t>e_bike_status_id</t>
+  </si>
+  <si>
+    <t>e_bike_status_name</t>
+  </si>
+  <si>
+    <t>is_listed</t>
+  </si>
+  <si>
+    <t>is_booked</t>
+  </si>
+  <si>
+    <t>issue</t>
+  </si>
+  <si>
+    <t>has_issue</t>
+  </si>
+  <si>
+    <t>feature_check</t>
+  </si>
+  <si>
+    <t>feature_check_id</t>
+  </si>
+  <si>
+    <t>feature_check_name</t>
+  </si>
+  <si>
+    <t>Battery charges and holds power</t>
+  </si>
+  <si>
+    <t>Motor assist functioning smoothly</t>
+  </si>
+  <si>
+    <t>Brakes responsive and reliable</t>
+  </si>
+  <si>
+    <t>Lights and indicators working</t>
+  </si>
+  <si>
+    <t>Display and controls operational</t>
+  </si>
+  <si>
+    <t>Tyres properly inflated, no damage</t>
+  </si>
+  <si>
+    <t>Frame, seat, pedals secure</t>
+  </si>
+  <si>
+    <t>e_bike_feature_check</t>
+  </si>
+  <si>
+    <t>checked_ok</t>
+  </si>
+  <si>
+    <t>booking</t>
+  </si>
+  <si>
+    <t>booking_id</t>
+  </si>
+  <si>
+    <t>from_date</t>
+  </si>
+  <si>
+    <t>to_date</t>
+  </si>
+  <si>
+    <t>booking_total_amount</t>
+  </si>
+  <si>
+    <t>rental_amount</t>
+  </si>
+  <si>
+    <t>issue_id</t>
+  </si>
+  <si>
+    <t>issue_image_link</t>
+  </si>
+  <si>
+    <t>issue_description</t>
+  </si>
+  <si>
+    <t>insurance_claim</t>
+  </si>
+  <si>
+    <t>insurance_claim_id</t>
+  </si>
+  <si>
+    <t>insurance_claim_details</t>
+  </si>
+  <si>
+    <t>handover</t>
+  </si>
+  <si>
+    <t>handover_id</t>
+  </si>
+  <si>
+    <t>handover_date_time</t>
+  </si>
+  <si>
+    <t>handover_location</t>
+  </si>
+  <si>
+    <t>pre_handover_image_link</t>
+  </si>
+  <si>
+    <t>return</t>
+  </si>
+  <si>
+    <t>return_id</t>
+  </si>
+  <si>
+    <t>return_date_time</t>
+  </si>
+  <si>
+    <t>return_location</t>
+  </si>
+  <si>
+    <t>return_image_link</t>
+  </si>
+  <si>
+    <t>geo_location</t>
+  </si>
+  <si>
+    <t>geo_location_type</t>
+  </si>
+  <si>
+    <t>geo_location_type_id</t>
+  </si>
+  <si>
+    <t>geo_location_type_name</t>
+  </si>
+  <si>
+    <t>geo_location_id</t>
+  </si>
+  <si>
+    <t>lattitude</t>
+  </si>
+  <si>
+    <t>longitude</t>
+  </si>
+  <si>
+    <t>geo_location_name</t>
+  </si>
+  <si>
+    <t>geo_location_details</t>
+  </si>
+  <si>
+    <t>geo_location_postal address</t>
+  </si>
+  <si>
+    <t>geo_location_start_date</t>
+  </si>
+  <si>
+    <t>geo_location_end_date</t>
+  </si>
+  <si>
+    <t>charging station</t>
+  </si>
+  <si>
+    <t>dedicated bike station</t>
+  </si>
+  <si>
+    <t>in_use</t>
+  </si>
+  <si>
+    <t>e_bike_rating_id</t>
+  </si>
+  <si>
+    <t>insurance_purchased</t>
+  </si>
+  <si>
+    <t>incident</t>
+  </si>
+  <si>
+    <t>issue_date_time</t>
+  </si>
+  <si>
+    <t>issue_feature_check</t>
+  </si>
+  <si>
+    <t>incident_id</t>
+  </si>
+  <si>
+    <t>incident_date</t>
+  </si>
+  <si>
+    <t>incident_image_link</t>
+  </si>
+  <si>
+    <t>incident_description</t>
+  </si>
+  <si>
+    <t>insurance_premium</t>
+  </si>
+  <si>
+    <t>booking_cancellation</t>
+  </si>
+  <si>
+    <t>booking_cancellation_id</t>
+  </si>
+  <si>
+    <t>cancelation_date</t>
+  </si>
+  <si>
+    <t>cancelation_charge</t>
+  </si>
+  <si>
+    <t>accounts</t>
+  </si>
+  <si>
+    <t>amount_credit</t>
+  </si>
+  <si>
+    <t>insurance premium payout</t>
+  </si>
+  <si>
+    <t>insurance premium received</t>
+  </si>
+  <si>
+    <t>supplier payout</t>
+  </si>
+  <si>
+    <t>rental received</t>
+  </si>
+  <si>
+    <t>cancellation pay to renter</t>
+  </si>
+  <si>
+    <t>issue pay to renter</t>
+  </si>
+  <si>
+    <t>incident pay to renter</t>
+  </si>
+  <si>
+    <t>accounts_id</t>
+  </si>
+  <si>
+    <t>accounts_type_id</t>
+  </si>
+  <si>
+    <t>accounts_type</t>
+  </si>
+  <si>
+    <t>accounts_type_name</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -175,8 +426,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -185,7 +444,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -202,15 +467,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -525,180 +789,564 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C79A3F5-2569-40DD-8568-D6589AE542AA}">
-  <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:N49"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="23.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.6640625" customWidth="1"/>
-    <col min="5" max="5" width="20.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.9296875" customWidth="1"/>
+    <col min="2" max="2" width="16.265625" customWidth="1"/>
+    <col min="3" max="3" width="4.19921875" customWidth="1"/>
+    <col min="4" max="4" width="16.265625" customWidth="1"/>
+    <col min="5" max="5" width="4.19921875" customWidth="1"/>
+    <col min="6" max="6" width="16.265625" customWidth="1"/>
+    <col min="7" max="7" width="4.19921875" customWidth="1"/>
+    <col min="8" max="8" width="16.265625" customWidth="1"/>
+    <col min="9" max="9" width="4.19921875" customWidth="1"/>
+    <col min="10" max="10" width="16.265625" customWidth="1"/>
+    <col min="11" max="11" width="4.19921875" customWidth="1"/>
+    <col min="12" max="12" width="16.265625" customWidth="1"/>
+    <col min="13" max="13" width="4.19921875" customWidth="1"/>
+    <col min="14" max="14" width="16.265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="2" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B11" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="J17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D18" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F3" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" t="s">
-        <v>34</v>
-      </c>
-      <c r="G5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="G6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>12</v>
+      <c r="L18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J19" s="1"/>
+      <c r="L19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B20" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J20" s="1"/>
+      <c r="L20" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B21" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J21" s="1"/>
+      <c r="L21" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="B22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="F23" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="F24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="F25" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D27" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D28" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D29" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D30" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D31" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="F32" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="F33" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="F34" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="F35" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="F36" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="F37" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B40" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B41" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B42" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B43" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B44" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B45" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="L45" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="J46" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="J47" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="J48" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="10:10" x14ac:dyDescent="0.45">
+      <c r="J49" s="3" t="s">
+        <v>93</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/BusinessAnalysis/database_design.xlsx
+++ b/BusinessAnalysis/database_design.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="146">
   <si>
     <t>user</t>
   </si>
@@ -152,9 +152,6 @@
     <t>tnc_accepted</t>
   </si>
   <si>
-    <t>pick_up_address</t>
-  </si>
-  <si>
     <t>e_bike_status</t>
   </si>
   <si>
@@ -405,13 +402,82 @@
   </si>
   <si>
     <t>accounts_type_name</t>
+  </si>
+  <si>
+    <t>pick_up_geo_location_id</t>
+  </si>
+  <si>
+    <t>pickup location</t>
+  </si>
+  <si>
+    <t>insurance_plan</t>
+  </si>
+  <si>
+    <t>insurance_plan_id</t>
+  </si>
+  <si>
+    <t>insurer</t>
+  </si>
+  <si>
+    <t>insurer_id</t>
+  </si>
+  <si>
+    <t>insurer_name</t>
+  </si>
+  <si>
+    <t>insurance_plan_name</t>
+  </si>
+  <si>
+    <t>insurance_plan_description</t>
+  </si>
+  <si>
+    <t>insurance_claim_amount</t>
+  </si>
+  <si>
+    <t>insured_id</t>
+  </si>
+  <si>
+    <t>insurance_policy</t>
+  </si>
+  <si>
+    <t>insurence_policy_id</t>
+  </si>
+  <si>
+    <t>insurance_policy_id</t>
+  </si>
+  <si>
+    <t>date_of_purchase</t>
+  </si>
+  <si>
+    <t>date_effective_from</t>
+  </si>
+  <si>
+    <t>date_effective_to</t>
+  </si>
+  <si>
+    <t>insurance_claim_date</t>
+  </si>
+  <si>
+    <t>premium_amount</t>
+  </si>
+  <si>
+    <t>sum_assured</t>
+  </si>
+  <si>
+    <t>premium_per_week</t>
+  </si>
+  <si>
+    <t>exclusion_rules</t>
+  </si>
+  <si>
+    <t>booking_date</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,8 +500,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="8" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="8" tint="-0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -454,6 +543,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -467,7 +562,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -476,6 +571,11 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -790,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:N49"/>
+  <dimension ref="B2:N52"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3.9296875" customWidth="1"/>
@@ -807,6 +907,7 @@
     <col min="12" max="12" width="16.265625" customWidth="1"/>
     <col min="13" max="13" width="4.19921875" customWidth="1"/>
     <col min="14" max="14" width="16.265625" customWidth="1"/>
+    <col min="15" max="15" width="4.3984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.45">
@@ -852,7 +953,7 @@
         <v>27</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.45">
@@ -875,7 +976,7 @@
         <v>23</v>
       </c>
       <c r="N4" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.45">
@@ -956,7 +1057,7 @@
         <v>6</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>35</v>
@@ -967,7 +1068,7 @@
         <v>10</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J11" s="4" t="s">
         <v>36</v>
@@ -977,82 +1078,85 @@
       <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="H12" s="9" t="s">
+        <v>126</v>
+      </c>
       <c r="J12" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B16" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>21</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N16" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B17" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>9</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>9</v>
       </c>
       <c r="N17" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.45">
       <c r="D18" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>21</v>
@@ -1061,288 +1165,375 @@
         <v>21</v>
       </c>
       <c r="N18" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B19" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J19" s="1"/>
       <c r="L19" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N19" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B20" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J20" s="1"/>
       <c r="L20" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B21" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>98</v>
+        <v>52</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>97</v>
       </c>
       <c r="J21" s="1"/>
       <c r="L21" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.45">
       <c r="B22" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.45">
       <c r="F23" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>106</v>
+        <v>54</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.45">
       <c r="F24" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.45">
       <c r="F25" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D27" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>122</v>
+        <v>56</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="H26" s="9" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.45">
-      <c r="D28" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F28" s="3" t="s">
+      <c r="D28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>121</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="I28" s="7"/>
+      <c r="J28" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.45">
       <c r="D29" s="3" t="s">
-        <v>61</v>
+        <v>107</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="I29" s="7"/>
+      <c r="J29" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="L29" s="9" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.45">
       <c r="D30" s="3" t="s">
-        <v>109</v>
+        <v>60</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H30" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="I30" s="7"/>
+      <c r="J30" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.45">
       <c r="D31" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>116</v>
+        <v>108</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
+      <c r="L31" s="9" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="32" spans="2:14" x14ac:dyDescent="0.45">
+      <c r="D32" s="3" t="s">
+        <v>109</v>
+      </c>
       <c r="F32" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="I32" s="7"/>
+      <c r="J32" s="7"/>
+      <c r="L32" s="9" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.45">
       <c r="F33" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.45">
       <c r="F34" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
+      </c>
+      <c r="H34" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.45">
       <c r="F35" s="4" t="s">
-        <v>117</v>
+        <v>112</v>
+      </c>
+      <c r="H35" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.45">
       <c r="F36" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
+      </c>
+      <c r="L36" s="9" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.45">
       <c r="F37" s="4" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B40" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J40" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="F38" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B43" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L43" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="L40" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B41" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B42" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="B43" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B44" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>104</v>
+        <v>101</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>94</v>
+        <v>85</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.45">
       <c r="B45" s="3" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>105</v>
+        <v>60</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="J45" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="L45" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="L45" s="4" t="s">
-        <v>95</v>
-      </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B46" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>70</v>
+      </c>
       <c r="J46" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B47" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="L47" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.45">
+      <c r="B48" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="49" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="H49" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="L49" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="50" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="J50" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="J47" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.45">
-      <c r="J48" s="3" t="s">
+    <row r="51" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="J51" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="52" spans="8:12" x14ac:dyDescent="0.45">
+      <c r="J52" s="3" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="49" spans="10:10" x14ac:dyDescent="0.45">
-      <c r="J49" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
